--- a/Financial Freedom Calculator and Scenarios.xlsx
+++ b/Financial Freedom Calculator and Scenarios.xlsx
@@ -551,7 +551,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="4">
-        <v>4000000.0</v>
+        <v>100.0</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="3" t="s">
@@ -621,19 +621,19 @@
         <v>10</v>
       </c>
       <c r="C5" s="7">
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="8">
         <f>($C$4*12)/$C$9</f>
-        <v>0.0690294887</v>
+        <v>0.07068592743</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="8">
         <f>(1+C5)/(1-G5)-1</f>
-        <v>0.1600797092</v>
+        <v>0.1567671595</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -641,12 +641,12 @@
       <c r="M5" s="1"/>
       <c r="N5" s="8">
         <f>($C$4*12)/$C$9</f>
-        <v>0.0690294887</v>
+        <v>0.07068592743</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="8">
         <f>($I$10/$O$6)-1</f>
-        <v>1.469328077</v>
+        <v>1.435629326</v>
       </c>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
@@ -654,12 +654,12 @@
       <c r="T5" s="1"/>
       <c r="U5" s="8">
         <f>($C$4*12)/$C$9</f>
-        <v>0.0690294887</v>
+        <v>0.07068592743</v>
       </c>
       <c r="V5" s="1"/>
       <c r="W5" s="8">
         <f>P$5*2</f>
-        <v>2.938656154</v>
+        <v>2.871258652</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="3" t="s">
@@ -688,19 +688,19 @@
       </c>
       <c r="F6" s="9">
         <f>$C$9</f>
-        <v>695354998.4</v>
+        <v>16976.50499</v>
       </c>
       <c r="G6" s="9">
         <f t="shared" ref="G6:G30" si="1">F6*G$5</f>
-        <v>48000000</v>
+        <v>1200</v>
       </c>
       <c r="H6" s="9">
         <f t="shared" ref="H6:H30" si="2">F6-G6</f>
-        <v>647354998.4</v>
+        <v>15776.50499</v>
       </c>
       <c r="I6" s="9">
         <f t="shared" ref="I6:I30" si="3">H6*(1+$I$5)</f>
-        <v>750983398.2</v>
+        <v>18249.74287</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -710,19 +710,19 @@
       </c>
       <c r="M6" s="9">
         <f>$C$9</f>
-        <v>695354998.4</v>
+        <v>16976.50499</v>
       </c>
       <c r="N6" s="9">
         <f t="shared" ref="N6:N10" si="4">(M6*N$5)*((1+$C$5)^5-1)/$C$5</f>
-        <v>281596846.1</v>
+        <v>6970.069219</v>
       </c>
       <c r="O6" s="9">
         <f t="shared" ref="O6:O10" si="5">M6-N6</f>
-        <v>413758152.3</v>
+        <v>10006.43578</v>
       </c>
       <c r="P6" s="11">
         <f t="shared" ref="P6:P10" si="6">O6*(1+P$5)</f>
-        <v>1021704622</v>
+        <v>24371.96843</v>
       </c>
       <c r="Q6" s="12">
         <f>P$6/$I$10-1</f>
@@ -735,35 +735,35 @@
       </c>
       <c r="T6" s="9">
         <f>$C$9</f>
-        <v>695354998.4</v>
+        <v>16976.50499</v>
       </c>
       <c r="U6" s="9">
         <f t="shared" ref="U6:U10" si="7">(T6*U$5)*((1+$C$5)^5-1)/$C$5</f>
-        <v>281596846.1</v>
+        <v>6970.069219</v>
       </c>
       <c r="V6" s="9">
         <f t="shared" ref="V6:V10" si="8">T6-U6</f>
-        <v>413758152.3</v>
+        <v>10006.43578</v>
       </c>
       <c r="W6" s="11">
         <f t="shared" ref="W6:W10" si="9">V6*(1+W$5)</f>
-        <v>1629651093</v>
+        <v>38737.50108</v>
       </c>
       <c r="X6" s="12">
         <f>W$6/$I$10-1</f>
-        <v>0.5950315353</v>
+        <v>0.5894284942</v>
       </c>
       <c r="Y6" s="9">
         <f t="shared" ref="Y6:Y10" si="10">P6</f>
-        <v>1021704622</v>
+        <v>24371.96843</v>
       </c>
       <c r="Z6" s="9">
         <f t="shared" ref="Z6:Z10" si="11">(W6-P6)*50%</f>
-        <v>303973235.1</v>
+        <v>7182.766325</v>
       </c>
       <c r="AA6" s="9">
         <f t="shared" ref="AA6:AA10" si="12">(W6-P6)*50%</f>
-        <v>303973235.1</v>
+        <v>7182.766325</v>
       </c>
       <c r="AB6" s="1"/>
     </row>
@@ -779,23 +779,23 @@
       </c>
       <c r="F7" s="9">
         <f t="shared" ref="F7:F30" si="13">I6</f>
-        <v>750983398.2</v>
+        <v>18249.74287</v>
       </c>
       <c r="G7" s="9">
         <f t="shared" si="1"/>
-        <v>51840000</v>
+        <v>1290</v>
       </c>
       <c r="H7" s="9">
         <f t="shared" si="2"/>
-        <v>699143398.2</v>
+        <v>16959.74287</v>
       </c>
       <c r="I7" s="9">
         <f t="shared" si="3"/>
-        <v>811062070.1</v>
+        <v>19618.47358</v>
       </c>
       <c r="J7" s="12">
         <f t="shared" ref="J7:J30" si="14">G7/G6-1</f>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="10" t="s">
@@ -803,19 +803,19 @@
       </c>
       <c r="M7" s="9">
         <f t="shared" ref="M7:M10" si="15">P6</f>
-        <v>1021704622</v>
+        <v>24371.96843</v>
       </c>
       <c r="N7" s="9">
         <f t="shared" si="4"/>
-        <v>413758152.3</v>
+        <v>10006.43578</v>
       </c>
       <c r="O7" s="9">
         <f t="shared" si="5"/>
-        <v>607946470.2</v>
+        <v>14365.53265</v>
       </c>
       <c r="P7" s="13">
         <f t="shared" si="6"/>
-        <v>1501219288</v>
+        <v>34989.11261</v>
       </c>
       <c r="Q7" s="12">
         <f>P$7/$I$15-1</f>
@@ -827,35 +827,35 @@
       </c>
       <c r="T7" s="9">
         <f t="shared" ref="T7:T10" si="16">Y6</f>
-        <v>1021704622</v>
+        <v>24371.96843</v>
       </c>
       <c r="U7" s="9">
         <f t="shared" si="7"/>
-        <v>413758152.3</v>
+        <v>10006.43578</v>
       </c>
       <c r="V7" s="9">
         <f t="shared" si="8"/>
-        <v>607946470.2</v>
+        <v>14365.53265</v>
       </c>
       <c r="W7" s="13">
         <f t="shared" si="9"/>
-        <v>2394492106</v>
+        <v>55612.69257</v>
       </c>
       <c r="X7" s="12">
         <f>W$7/$I$15-1</f>
-        <v>0.5950315353</v>
+        <v>0.5894284942</v>
       </c>
       <c r="Y7" s="9">
         <f t="shared" si="10"/>
-        <v>1501219288</v>
+        <v>34989.11261</v>
       </c>
       <c r="Z7" s="9">
         <f t="shared" si="11"/>
-        <v>446636408.9</v>
+        <v>10311.78998</v>
       </c>
       <c r="AA7" s="9">
         <f t="shared" si="12"/>
-        <v>446636408.9</v>
+        <v>10311.78998</v>
       </c>
       <c r="AB7" s="1"/>
     </row>
@@ -871,23 +871,23 @@
       </c>
       <c r="F8" s="9">
         <f t="shared" si="13"/>
-        <v>811062070.1</v>
+        <v>19618.47358</v>
       </c>
       <c r="G8" s="9">
         <f t="shared" si="1"/>
-        <v>55987200</v>
+        <v>1386.75</v>
       </c>
       <c r="H8" s="9">
         <f t="shared" si="2"/>
-        <v>755074870.1</v>
+        <v>18231.72358</v>
       </c>
       <c r="I8" s="9">
         <f t="shared" si="3"/>
-        <v>875947035.7</v>
+        <v>21089.8591</v>
       </c>
       <c r="J8" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="10" t="s">
@@ -895,19 +895,19 @@
       </c>
       <c r="M8" s="9">
         <f t="shared" si="15"/>
-        <v>1501219288</v>
+        <v>34989.11261</v>
       </c>
       <c r="N8" s="9">
         <f t="shared" si="4"/>
-        <v>607946470.2</v>
+        <v>14365.53265</v>
       </c>
       <c r="O8" s="9">
         <f t="shared" si="5"/>
-        <v>893272817.8</v>
+        <v>20623.57996</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="6"/>
-        <v>2205783649</v>
+        <v>50231.39616</v>
       </c>
       <c r="Q8" s="12">
         <f>P$8/$I$20-1</f>
@@ -919,35 +919,35 @@
       </c>
       <c r="T8" s="9">
         <f t="shared" si="16"/>
-        <v>1501219288</v>
+        <v>34989.11261</v>
       </c>
       <c r="U8" s="9">
         <f t="shared" si="7"/>
-        <v>607946470.2</v>
+        <v>14365.53265</v>
       </c>
       <c r="V8" s="9">
         <f t="shared" si="8"/>
-        <v>893272817.8</v>
+        <v>20623.57996</v>
       </c>
       <c r="W8" s="14">
         <f t="shared" si="9"/>
-        <v>3518294481</v>
+        <v>79839.21236</v>
       </c>
       <c r="X8" s="12">
         <f>W$8/$I$20-1</f>
-        <v>0.5950315353</v>
+        <v>0.5894284942</v>
       </c>
       <c r="Y8" s="9">
         <f t="shared" si="10"/>
-        <v>2205783649</v>
+        <v>50231.39616</v>
       </c>
       <c r="Z8" s="9">
         <f t="shared" si="11"/>
-        <v>656255415.7</v>
+        <v>14803.9081</v>
       </c>
       <c r="AA8" s="9">
         <f t="shared" si="12"/>
-        <v>656255415.7</v>
+        <v>14803.9081</v>
       </c>
       <c r="AB8" s="1"/>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="C9" s="4">
         <f>IF(OR(C7="", C8=""), C4*12*((1+C5)^C6-1)/C5, C4*(1+C5)^(C8-(YEAR(TODAY())-C7))*12*((1+C5)^C6-1)/C5)</f>
-        <v>695354998.4</v>
+        <v>16976.50499</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="5">
@@ -966,23 +966,23 @@
       </c>
       <c r="F9" s="9">
         <f t="shared" si="13"/>
-        <v>875947035.7</v>
+        <v>21089.8591</v>
       </c>
       <c r="G9" s="9">
         <f t="shared" si="1"/>
-        <v>60466176</v>
+        <v>1490.75625</v>
       </c>
       <c r="H9" s="9">
         <f t="shared" si="2"/>
-        <v>815480859.7</v>
+        <v>19599.10285</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="3"/>
-        <v>946022798.6</v>
+        <v>22671.59854</v>
       </c>
       <c r="J9" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="15" t="s">
@@ -990,19 +990,19 @@
       </c>
       <c r="M9" s="9">
         <f t="shared" si="15"/>
-        <v>2205783649</v>
+        <v>50231.39616</v>
       </c>
       <c r="N9" s="9">
         <f t="shared" si="4"/>
-        <v>893272817.8</v>
+        <v>20623.57996</v>
       </c>
       <c r="O9" s="9">
         <f t="shared" si="5"/>
-        <v>1312510831</v>
+        <v>29607.8162</v>
       </c>
       <c r="P9" s="16">
         <f t="shared" si="6"/>
-        <v>3241019847</v>
+        <v>72113.66542</v>
       </c>
       <c r="Q9" s="12">
         <f>P$9/$I$25-1</f>
@@ -1014,35 +1014,35 @@
       </c>
       <c r="T9" s="9">
         <f t="shared" si="16"/>
-        <v>2205783649</v>
+        <v>50231.39616</v>
       </c>
       <c r="U9" s="9">
         <f t="shared" si="7"/>
-        <v>893272817.8</v>
+        <v>20623.57996</v>
       </c>
       <c r="V9" s="9">
         <f t="shared" si="8"/>
-        <v>1312510831</v>
+        <v>29607.8162</v>
       </c>
       <c r="W9" s="16">
         <f t="shared" si="9"/>
-        <v>5169528863</v>
+        <v>114619.5146</v>
       </c>
       <c r="X9" s="12">
         <f>W$9/$I$25-1</f>
-        <v>0.5950315353</v>
+        <v>0.5894284942</v>
       </c>
       <c r="Y9" s="9">
         <f t="shared" si="10"/>
-        <v>3241019847</v>
+        <v>72113.66542</v>
       </c>
       <c r="Z9" s="9">
         <f t="shared" si="11"/>
-        <v>964254507.9</v>
+        <v>21252.92461</v>
       </c>
       <c r="AA9" s="9">
         <f t="shared" si="12"/>
-        <v>964254507.9</v>
+        <v>21252.92461</v>
       </c>
       <c r="AB9" s="1"/>
     </row>
@@ -1056,23 +1056,23 @@
       </c>
       <c r="F10" s="9">
         <f t="shared" si="13"/>
-        <v>946022798.6</v>
+        <v>22671.59854</v>
       </c>
       <c r="G10" s="9">
         <f t="shared" si="1"/>
-        <v>65303470.08</v>
+        <v>1602.562969</v>
       </c>
       <c r="H10" s="9">
         <f t="shared" si="2"/>
-        <v>880719328.5</v>
+        <v>21069.03557</v>
       </c>
       <c r="I10" s="11">
         <f t="shared" si="3"/>
-        <v>1021704622</v>
+        <v>24371.96843</v>
       </c>
       <c r="J10" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="15" t="s">
@@ -1080,19 +1080,19 @@
       </c>
       <c r="M10" s="9">
         <f t="shared" si="15"/>
-        <v>3241019847</v>
+        <v>72113.66542</v>
       </c>
       <c r="N10" s="9">
         <f t="shared" si="4"/>
-        <v>1312510831</v>
+        <v>29607.8162</v>
       </c>
       <c r="O10" s="9">
         <f t="shared" si="5"/>
-        <v>1928509016</v>
+        <v>42505.84922</v>
       </c>
       <c r="P10" s="17">
         <f t="shared" si="6"/>
-        <v>4762121459</v>
+        <v>103528.4929</v>
       </c>
       <c r="Q10" s="12">
         <f>P$10/$I$30-1</f>
@@ -1104,35 +1104,35 @@
       </c>
       <c r="T10" s="9">
         <f t="shared" si="16"/>
-        <v>3241019847</v>
+        <v>72113.66542</v>
       </c>
       <c r="U10" s="9">
         <f t="shared" si="7"/>
-        <v>1312510831</v>
+        <v>29607.8162</v>
       </c>
       <c r="V10" s="9">
         <f t="shared" si="8"/>
-        <v>1928509016</v>
+        <v>42505.84922</v>
       </c>
       <c r="W10" s="17">
         <f t="shared" si="9"/>
-        <v>7595733902</v>
+        <v>164551.1366</v>
       </c>
       <c r="X10" s="12">
         <f>W$10/$I$30-1</f>
-        <v>0.5950315353</v>
+        <v>0.5894284942</v>
       </c>
       <c r="Y10" s="9">
         <f t="shared" si="10"/>
-        <v>4762121459</v>
+        <v>103528.4929</v>
       </c>
       <c r="Z10" s="9">
         <f t="shared" si="11"/>
-        <v>1416806222</v>
+        <v>30511.32184</v>
       </c>
       <c r="AA10" s="9">
         <f t="shared" si="12"/>
-        <v>1416806222</v>
+        <v>30511.32184</v>
       </c>
       <c r="AB10" s="1"/>
     </row>
@@ -1148,23 +1148,23 @@
       </c>
       <c r="F11" s="9">
         <f t="shared" si="13"/>
-        <v>1021704622</v>
+        <v>24371.96843</v>
       </c>
       <c r="G11" s="9">
         <f t="shared" si="1"/>
-        <v>70527747.69</v>
+        <v>1722.755191</v>
       </c>
       <c r="H11" s="9">
         <f t="shared" si="2"/>
-        <v>951176874.8</v>
+        <v>22649.21323</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="3"/>
-        <v>1103440992</v>
+        <v>26199.86606</v>
       </c>
       <c r="J11" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="18"/>
@@ -1195,23 +1195,23 @@
       </c>
       <c r="F12" s="9">
         <f t="shared" si="13"/>
-        <v>1103440992</v>
+        <v>26199.86606</v>
       </c>
       <c r="G12" s="9">
         <f t="shared" si="1"/>
-        <v>76169967.5</v>
+        <v>1851.961831</v>
       </c>
       <c r="H12" s="9">
         <f t="shared" si="2"/>
-        <v>1027271025</v>
+        <v>24347.90423</v>
       </c>
       <c r="I12" s="9">
         <f t="shared" si="3"/>
-        <v>1191716272</v>
+        <v>28164.85601</v>
       </c>
       <c r="J12" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K12" s="18"/>
       <c r="L12" s="3" t="s">
@@ -1250,23 +1250,23 @@
       </c>
       <c r="F13" s="9">
         <f t="shared" si="13"/>
-        <v>1191716272</v>
+        <v>28164.85601</v>
       </c>
       <c r="G13" s="9">
         <f t="shared" si="1"/>
-        <v>82263564.9</v>
+        <v>1990.858968</v>
       </c>
       <c r="H13" s="9">
         <f t="shared" si="2"/>
-        <v>1109452707</v>
+        <v>26173.99704</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="3"/>
-        <v>1287053573</v>
+        <v>30277.22021</v>
       </c>
       <c r="J13" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K13" s="18"/>
       <c r="L13" s="18"/>
@@ -1297,23 +1297,23 @@
       </c>
       <c r="F14" s="9">
         <f t="shared" si="13"/>
-        <v>1287053573</v>
+        <v>30277.22021</v>
       </c>
       <c r="G14" s="9">
         <f t="shared" si="1"/>
-        <v>88844650.09</v>
+        <v>2140.173391</v>
       </c>
       <c r="H14" s="9">
         <f t="shared" si="2"/>
-        <v>1198208923</v>
+        <v>28137.04682</v>
       </c>
       <c r="I14" s="9">
         <f t="shared" si="3"/>
-        <v>1390017859</v>
+        <v>32548.01173</v>
       </c>
       <c r="J14" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K14" s="18"/>
       <c r="L14" s="18"/>
@@ -1344,23 +1344,23 @@
       </c>
       <c r="F15" s="9">
         <f t="shared" si="13"/>
-        <v>1390017859</v>
+        <v>32548.01173</v>
       </c>
       <c r="G15" s="9">
         <f t="shared" si="1"/>
-        <v>95952222.1</v>
+        <v>2300.686395</v>
       </c>
       <c r="H15" s="9">
         <f t="shared" si="2"/>
-        <v>1294065637</v>
+        <v>30247.32533</v>
       </c>
       <c r="I15" s="13">
         <f t="shared" si="3"/>
-        <v>1501219288</v>
+        <v>34989.11261</v>
       </c>
       <c r="J15" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K15" s="18"/>
       <c r="L15" s="18"/>
@@ -1391,23 +1391,23 @@
       </c>
       <c r="F16" s="9">
         <f t="shared" si="13"/>
-        <v>1501219288</v>
+        <v>34989.11261</v>
       </c>
       <c r="G16" s="9">
         <f t="shared" si="1"/>
-        <v>103628399.9</v>
+        <v>2473.237875</v>
       </c>
       <c r="H16" s="9">
         <f t="shared" si="2"/>
-        <v>1397590888</v>
+        <v>32515.87473</v>
       </c>
       <c r="I16" s="9">
         <f t="shared" si="3"/>
-        <v>1621316831</v>
+        <v>37613.29605</v>
       </c>
       <c r="J16" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
@@ -1438,23 +1438,23 @@
       </c>
       <c r="F17" s="9">
         <f t="shared" si="13"/>
-        <v>1621316831</v>
+        <v>37613.29605</v>
       </c>
       <c r="G17" s="9">
         <f t="shared" si="1"/>
-        <v>111918671.9</v>
+        <v>2658.730715</v>
       </c>
       <c r="H17" s="9">
         <f t="shared" si="2"/>
-        <v>1509398159</v>
+        <v>34954.56534</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="3"/>
-        <v>1751022177</v>
+        <v>40434.29326</v>
       </c>
       <c r="J17" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K17" s="18"/>
       <c r="L17" s="18"/>
@@ -1485,23 +1485,23 @@
       </c>
       <c r="F18" s="9">
         <f t="shared" si="13"/>
-        <v>1751022177</v>
+        <v>40434.29326</v>
       </c>
       <c r="G18" s="9">
         <f t="shared" si="1"/>
-        <v>120872165.6</v>
+        <v>2858.135519</v>
       </c>
       <c r="H18" s="9">
         <f t="shared" si="2"/>
-        <v>1630150012</v>
+        <v>37576.15774</v>
       </c>
       <c r="I18" s="9">
         <f t="shared" si="3"/>
-        <v>1891103952</v>
+        <v>43466.86525</v>
       </c>
       <c r="J18" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
@@ -1532,23 +1532,23 @@
       </c>
       <c r="F19" s="9">
         <f t="shared" si="13"/>
-        <v>1891103952</v>
+        <v>43466.86525</v>
       </c>
       <c r="G19" s="9">
         <f t="shared" si="1"/>
-        <v>130541938.9</v>
+        <v>3072.495683</v>
       </c>
       <c r="H19" s="9">
         <f t="shared" si="2"/>
-        <v>1760562013</v>
+        <v>40394.36957</v>
       </c>
       <c r="I19" s="9">
         <f t="shared" si="3"/>
-        <v>2042392268</v>
+        <v>46726.88015</v>
       </c>
       <c r="J19" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K19" s="18"/>
       <c r="L19" s="18"/>
@@ -1579,23 +1579,23 @@
       </c>
       <c r="F20" s="9">
         <f t="shared" si="13"/>
-        <v>2042392268</v>
+        <v>46726.88015</v>
       </c>
       <c r="G20" s="9">
         <f t="shared" si="1"/>
-        <v>140985294</v>
+        <v>3302.932859</v>
       </c>
       <c r="H20" s="9">
         <f t="shared" si="2"/>
-        <v>1901406974</v>
+        <v>43423.94729</v>
       </c>
       <c r="I20" s="14">
         <f t="shared" si="3"/>
-        <v>2205783649</v>
+        <v>50231.39616</v>
       </c>
       <c r="J20" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K20" s="18"/>
       <c r="L20" s="18"/>
@@ -1626,23 +1626,23 @@
       </c>
       <c r="F21" s="9">
         <f t="shared" si="13"/>
-        <v>2205783649</v>
+        <v>50231.39616</v>
       </c>
       <c r="G21" s="9">
         <f t="shared" si="1"/>
-        <v>152264117.5</v>
+        <v>3550.652823</v>
       </c>
       <c r="H21" s="9">
         <f t="shared" si="2"/>
-        <v>2053519532</v>
+        <v>46680.74334</v>
       </c>
       <c r="I21" s="9">
         <f t="shared" si="3"/>
-        <v>2382246341</v>
+        <v>53998.75087</v>
       </c>
       <c r="J21" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K21" s="18"/>
       <c r="L21" s="18"/>
@@ -1673,23 +1673,23 @@
       </c>
       <c r="F22" s="9">
         <f t="shared" si="13"/>
-        <v>2382246341</v>
+        <v>53998.75087</v>
       </c>
       <c r="G22" s="9">
         <f t="shared" si="1"/>
-        <v>164445246.9</v>
+        <v>3816.951785</v>
       </c>
       <c r="H22" s="9">
         <f t="shared" si="2"/>
-        <v>2217801094</v>
+        <v>50181.79909</v>
       </c>
       <c r="I22" s="9">
         <f t="shared" si="3"/>
-        <v>2572826048</v>
+        <v>58048.65719</v>
       </c>
       <c r="J22" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K22" s="18"/>
       <c r="L22" s="18"/>
@@ -1720,23 +1720,23 @@
       </c>
       <c r="F23" s="9">
         <f t="shared" si="13"/>
-        <v>2572826048</v>
+        <v>58048.65719</v>
       </c>
       <c r="G23" s="9">
         <f t="shared" si="1"/>
-        <v>177600866.6</v>
+        <v>4103.223169</v>
       </c>
       <c r="H23" s="9">
         <f t="shared" si="2"/>
-        <v>2395225182</v>
+        <v>53945.43402</v>
       </c>
       <c r="I23" s="9">
         <f t="shared" si="3"/>
-        <v>2778652132</v>
+        <v>62402.30647</v>
       </c>
       <c r="J23" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K23" s="18"/>
       <c r="L23" s="18"/>
@@ -1767,23 +1767,23 @@
       </c>
       <c r="F24" s="9">
         <f t="shared" si="13"/>
-        <v>2778652132</v>
+        <v>62402.30647</v>
       </c>
       <c r="G24" s="9">
         <f t="shared" si="1"/>
-        <v>191808936</v>
+        <v>4410.964907</v>
       </c>
       <c r="H24" s="9">
         <f t="shared" si="2"/>
-        <v>2586843196</v>
+        <v>57991.34157</v>
       </c>
       <c r="I24" s="9">
         <f t="shared" si="3"/>
-        <v>3000944303</v>
+        <v>67082.47946</v>
       </c>
       <c r="J24" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K24" s="18"/>
       <c r="L24" s="18"/>
@@ -1814,23 +1814,23 @@
       </c>
       <c r="F25" s="9">
         <f t="shared" si="13"/>
-        <v>3000944303</v>
+        <v>67082.47946</v>
       </c>
       <c r="G25" s="9">
         <f t="shared" si="1"/>
-        <v>207153650.8</v>
+        <v>4741.787275</v>
       </c>
       <c r="H25" s="9">
         <f t="shared" si="2"/>
-        <v>2793790652</v>
+        <v>62340.69219</v>
       </c>
       <c r="I25" s="16">
         <f t="shared" si="3"/>
-        <v>3241019847</v>
+        <v>72113.66542</v>
       </c>
       <c r="J25" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K25" s="18"/>
       <c r="L25" s="18"/>
@@ -1861,23 +1861,23 @@
       </c>
       <c r="F26" s="9">
         <f t="shared" si="13"/>
-        <v>3241019847</v>
+        <v>72113.66542</v>
       </c>
       <c r="G26" s="9">
         <f t="shared" si="1"/>
-        <v>223725942.9</v>
+        <v>5097.42132</v>
       </c>
       <c r="H26" s="9">
         <f t="shared" si="2"/>
-        <v>3017293904</v>
+        <v>67016.2441</v>
       </c>
       <c r="I26" s="9">
         <f t="shared" si="3"/>
-        <v>3500301435</v>
+        <v>77522.19033</v>
       </c>
       <c r="J26" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K26" s="18"/>
       <c r="L26" s="18"/>
@@ -1908,23 +1908,23 @@
       </c>
       <c r="F27" s="9">
         <f t="shared" si="13"/>
-        <v>3500301435</v>
+        <v>77522.19033</v>
       </c>
       <c r="G27" s="9">
         <f t="shared" si="1"/>
-        <v>241624018.3</v>
+        <v>5479.727919</v>
       </c>
       <c r="H27" s="9">
         <f t="shared" si="2"/>
-        <v>3258677417</v>
+        <v>72042.46241</v>
       </c>
       <c r="I27" s="9">
         <f t="shared" si="3"/>
-        <v>3780325550</v>
+        <v>83336.3546</v>
       </c>
       <c r="J27" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K27" s="18"/>
       <c r="L27" s="18"/>
@@ -1955,23 +1955,23 @@
       </c>
       <c r="F28" s="9">
         <f t="shared" si="13"/>
-        <v>3780325550</v>
+        <v>83336.3546</v>
       </c>
       <c r="G28" s="9">
         <f t="shared" si="1"/>
-        <v>260953939.8</v>
+        <v>5890.707513</v>
       </c>
       <c r="H28" s="9">
         <f t="shared" si="2"/>
-        <v>3519371610</v>
+        <v>77445.64709</v>
       </c>
       <c r="I28" s="9">
         <f t="shared" si="3"/>
-        <v>4082751594</v>
+        <v>89586.5812</v>
       </c>
       <c r="J28" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K28" s="18"/>
       <c r="L28" s="18"/>
@@ -2002,23 +2002,23 @@
       </c>
       <c r="F29" s="9">
         <f t="shared" si="13"/>
-        <v>4082751594</v>
+        <v>89586.5812</v>
       </c>
       <c r="G29" s="9">
         <f t="shared" si="1"/>
-        <v>281830255</v>
+        <v>6332.510577</v>
       </c>
       <c r="H29" s="9">
         <f t="shared" si="2"/>
-        <v>3800921339</v>
+        <v>83254.07062</v>
       </c>
       <c r="I29" s="9">
         <f t="shared" si="3"/>
-        <v>4409371721</v>
+        <v>96305.57479</v>
       </c>
       <c r="J29" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K29" s="18"/>
       <c r="L29" s="18"/>
@@ -2049,23 +2049,23 @@
       </c>
       <c r="F30" s="9">
         <f t="shared" si="13"/>
-        <v>4409371721</v>
+        <v>96305.57479</v>
       </c>
       <c r="G30" s="9">
         <f t="shared" si="1"/>
-        <v>304376675.4</v>
+        <v>6807.44887</v>
       </c>
       <c r="H30" s="9">
         <f t="shared" si="2"/>
-        <v>4104995046</v>
+        <v>89498.12592</v>
       </c>
       <c r="I30" s="17">
         <f t="shared" si="3"/>
-        <v>4762121459</v>
+        <v>103528.4929</v>
       </c>
       <c r="J30" s="12">
         <f t="shared" si="14"/>
-        <v>0.08</v>
+        <v>0.075</v>
       </c>
       <c r="K30" s="18"/>
       <c r="L30" s="18"/>
